--- a/data/trans_camb/LAWTONB_2R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 19,48</t>
+          <t>-17,57; 16,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 3,7</t>
+          <t>-23,28; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 2,56</t>
+          <t>-21,16; 3,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,67; -9,57</t>
+          <t>-53,24; -9,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 7,22</t>
+          <t>-42,6; 5,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,2; -2,52</t>
+          <t>-41,37; -1,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 3,27</t>
+          <t>-25,21; 3,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 1,09</t>
+          <t>-24,19; 1,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,87; -1,05</t>
+          <t>-23,71; -2,13</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 199,41</t>
+          <t>-66,5; 144,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,18; 41,06</t>
+          <t>-82,24; 40,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,63; 28,37</t>
+          <t>-70,29; 38,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-93,44; -18,94</t>
+          <t>-93,04; -19,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 33,5</t>
+          <t>-77,33; 18,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,54; -7,23</t>
+          <t>-68,1; -1,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,63; 23,67</t>
+          <t>-72,13; 22,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 12,55</t>
+          <t>-70,98; 11,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,92; -5,6</t>
+          <t>-63,13; -7,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 8,04</t>
+          <t>-22,71; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 14,5</t>
+          <t>-18,71; 12,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 6,78</t>
+          <t>-21,99; 6,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 46,73</t>
+          <t>-24,15; 41,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 47,58</t>
+          <t>-26,47; 49,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 20,03</t>
+          <t>-33,16; 20,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 13,88</t>
+          <t>-17,39; 13,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 15,95</t>
+          <t>-15,48; 15,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 8,37</t>
+          <t>-15,9; 8,14</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 64,55</t>
+          <t>-74,17; 62,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,62; 109,84</t>
+          <t>-60,15; 98,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 53,66</t>
+          <t>-60,59; 49,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 361,14</t>
+          <t>-48,96; 261,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 326,33</t>
+          <t>-57,13; 316,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,97; 158,49</t>
+          <t>-56,69; 152,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 81,67</t>
+          <t>-53,69; 84,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 86,82</t>
+          <t>-45,13; 93,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 54,85</t>
+          <t>-45,0; 51,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 8,53</t>
+          <t>-16,82; 9,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,97; -1,58</t>
+          <t>-24,92; -1,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 4,22</t>
+          <t>-18,85; 4,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 23,92</t>
+          <t>-20,77; 25,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 26,07</t>
+          <t>-22,35; 24,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 27,54</t>
+          <t>-13,88; 28,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 10,64</t>
+          <t>-12,77; 10,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 2,29</t>
+          <t>-19,08; 2,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 8,31</t>
+          <t>-12,06; 8,63</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 47,39</t>
+          <t>-50,78; 48,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,77; -7,97</t>
+          <t>-72,08; -5,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 23,98</t>
+          <t>-55,72; 27,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,56; 143,27</t>
+          <t>-42,38; 164,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 145,68</t>
+          <t>-47,4; 149,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 152,62</t>
+          <t>-28,42; 145,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,13; 51,89</t>
+          <t>-38,88; 55,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,49; 12,92</t>
+          <t>-55,84; 15,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 40,63</t>
+          <t>-33,2; 41,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 10,63</t>
+          <t>-6,14; 10,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 0,07</t>
+          <t>-14,29; -0,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 12,55</t>
+          <t>-1,76; 12,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 26,63</t>
+          <t>-4,66; 28,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 19,16</t>
+          <t>-8,49; 19,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 5,24</t>
+          <t>-35,66; 5,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 11,21</t>
+          <t>-3,28; 11,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 3,95</t>
+          <t>-9,53; 4,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 6,7</t>
+          <t>-21,02; 6,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 44,33</t>
+          <t>-19,63; 42,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 0,23</t>
+          <t>-45,48; -0,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 53,04</t>
+          <t>-5,33; 53,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 115,5</t>
+          <t>-13,99; 138,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 86,44</t>
+          <t>-24,55; 90,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,04; 22,84</t>
+          <t>-89,65; 28,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 44,46</t>
+          <t>-10,95; 48,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 16,06</t>
+          <t>-31,37; 18,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,91; 25,53</t>
+          <t>-69,12; 24,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 19,24</t>
+          <t>-10,8; 18,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 16,3</t>
+          <t>-10,64; 16,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 17,22</t>
+          <t>-9,51; 18,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 19,5</t>
+          <t>-5,73; 19,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 9,49</t>
+          <t>-16,28; 9,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 21,24</t>
+          <t>-0,62; 20,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 15,57</t>
+          <t>-4,11; 16,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 7,27</t>
+          <t>-11,15; 9,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 17,43</t>
+          <t>0,42; 17,26</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 89,79</t>
+          <t>-25,73; 99,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 74,71</t>
+          <t>-26,2; 86,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 86,97</t>
+          <t>-23,84; 88,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 66,07</t>
+          <t>-11,97; 70,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 31,72</t>
+          <t>-35,92; 33,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 73,33</t>
+          <t>-1,37; 69,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 54,85</t>
+          <t>-9,59; 56,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 25,0</t>
+          <t>-26,61; 33,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,1; 59,86</t>
+          <t>0,98; 62,72</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-96,53; 0,0</t>
+          <t>-75,71; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 85,13</t>
+          <t>-30,64; 84,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 9,46</t>
+          <t>-3,78; 10,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 9,91</t>
+          <t>-4,64; 9,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,99; 17,46</t>
+          <t>6,29; 18,24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 9,42</t>
+          <t>-3,8; 9,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 9,58</t>
+          <t>-4,06; 9,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,66; 18,05</t>
+          <t>6,38; 17,95</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 30,43</t>
+          <t>-9,81; 34,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 31,91</t>
+          <t>-12,23; 32,04</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,77; 57,48</t>
+          <t>17,01; 58,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 30,32</t>
+          <t>-10,06; 31,99</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 30,4</t>
+          <t>-10,93; 32,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,86; 59,51</t>
+          <t>16,83; 58,27</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 6,2</t>
+          <t>-5,05; 5,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -0,53</t>
+          <t>-10,52; -0,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 3,59</t>
+          <t>-5,52; 3,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 9,56</t>
+          <t>-1,43; 9,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 6,09</t>
+          <t>-4,55; 6,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 8,61</t>
+          <t>-19,29; 8,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,22</t>
+          <t>-1,2; 6,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 2,02</t>
+          <t>-5,2; 2,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 4,6</t>
+          <t>-12,23; 4,62</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 26,06</t>
+          <t>-17,64; 24,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-33,93; -2,18</t>
+          <t>-36,68; -1,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 15,56</t>
+          <t>-18,72; 16,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 29,77</t>
+          <t>-3,86; 29,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 19,56</t>
+          <t>-12,64; 19,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,85; 26,01</t>
+          <t>-51,88; 25,05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 21,45</t>
+          <t>-3,75; 22,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 6,93</t>
+          <t>-15,94; 9,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 15,13</t>
+          <t>-38,8; 15,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,02</t>
+          <t>-8,79</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-21,68</t>
+          <t>-22,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-11,98</t>
+          <t>-12,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 16,42</t>
+          <t>-16,29; 19,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 3,02</t>
+          <t>-22,25; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 3,14</t>
+          <t>-23,38; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,24; -9,17</t>
+          <t>-54,33; -9,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 5,51</t>
+          <t>-44,79; 4,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,37; -1,17</t>
+          <t>-42,36; -2,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 3,41</t>
+          <t>-24,28; 3,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 1,46</t>
+          <t>-25,44; 0,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-23,71; -2,13</t>
+          <t>-24,13; -3,04</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-41,45%</t>
+          <t>-45,45%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-48,18%</t>
+          <t>-50,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-42,98%</t>
+          <t>-46,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 144,31</t>
+          <t>-65,42; 185,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,24; 40,01</t>
+          <t>-81,7; 46,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,29; 38,15</t>
+          <t>-75,46; 17,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-93,04; -19,26</t>
+          <t>-94,0; -11,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 18,89</t>
+          <t>-77,93; 20,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,1; -1,99</t>
+          <t>-70,83; -6,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 22,23</t>
+          <t>-74,38; 22,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,98; 11,06</t>
+          <t>-71,97; 6,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,13; -7,11</t>
+          <t>-66,79; -15,49</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>-5,61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-4,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,59</t>
+          <t>-4,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 8,07</t>
+          <t>-22,55; 9,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 12,3</t>
+          <t>-18,7; 13,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 6,74</t>
+          <t>-21,84; 6,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 41,65</t>
+          <t>-24,14; 46,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 49,34</t>
+          <t>-25,6; 48,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 20,78</t>
+          <t>-34,79; 19,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 13,67</t>
+          <t>-16,88; 13,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 15,8</t>
+          <t>-14,99; 16,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 8,14</t>
+          <t>-16,35; 6,57</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-22,6%</t>
+          <t>-24,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,33%</t>
+          <t>-13,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-14,08%</t>
+          <t>-16,1%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-74,17; 62,22</t>
+          <t>-72,98; 80,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 98,11</t>
+          <t>-60,05; 107,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 49,87</t>
+          <t>-61,24; 52,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 261,84</t>
+          <t>-49,05; 318,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 316,04</t>
+          <t>-53,16; 344,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 152,21</t>
+          <t>-58,4; 154,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,69; 84,18</t>
+          <t>-51,69; 73,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 93,07</t>
+          <t>-43,74; 90,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 51,03</t>
+          <t>-45,94; 41,97</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>8,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-1,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 9,22</t>
+          <t>-18,28; 8,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-24,92; -1,35</t>
+          <t>-24,34; -1,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 4,8</t>
+          <t>-20,91; 2,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 25,58</t>
+          <t>-24,05; 20,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 24,63</t>
+          <t>-25,13; 24,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 28,35</t>
+          <t>-15,61; 28,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 10,73</t>
+          <t>-14,54; 8,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 2,58</t>
+          <t>-19,88; 2,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 8,63</t>
+          <t>-11,81; 9,39</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-26,49%</t>
+          <t>-28,26%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,25%</t>
+          <t>-5,04%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 48,3</t>
+          <t>-52,7; 44,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-72,08; -5,8</t>
+          <t>-71,16; -7,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,72; 27,49</t>
+          <t>-59,15; 16,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 164,8</t>
+          <t>-49,85; 115,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 149,81</t>
+          <t>-53,93; 126,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 145,1</t>
+          <t>-29,7; 167,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 55,74</t>
+          <t>-42,47; 37,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 15,15</t>
+          <t>-54,33; 14,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 41,44</t>
+          <t>-33,46; 46,87</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-16,59</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,08</t>
+          <t>4,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 10,0</t>
+          <t>-6,66; 10,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,29; -0,4</t>
+          <t>-14,78; -0,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 12,67</t>
+          <t>-2,02; 11,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 28,0</t>
+          <t>-3,89; 27,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 19,53</t>
+          <t>-8,19; 21,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 5,29</t>
+          <t>-8,19; 14,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 11,75</t>
+          <t>-3,54; 11,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 4,34</t>
+          <t>-9,9; 3,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,02; 6,55</t>
+          <t>-1,27; 10,46</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-58,34%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-25,31%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 42,67</t>
+          <t>-21,74; 41,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,48; -0,42</t>
+          <t>-48,2; -1,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 53,51</t>
+          <t>-6,5; 50,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 138,78</t>
+          <t>-12,6; 129,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 90,09</t>
+          <t>-24,05; 107,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,65; 28,95</t>
+          <t>-21,64; 70,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 48,16</t>
+          <t>-12,0; 45,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 18,85</t>
+          <t>-31,8; 13,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-69,12; 24,75</t>
+          <t>-4,0; 43,63</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,47</t>
+          <t>10,78</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 18,85</t>
+          <t>-11,29; 19,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 16,23</t>
+          <t>-10,55; 16,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 18,01</t>
+          <t>-9,44; 18,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 19,36</t>
+          <t>-6,27; 18,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 9,98</t>
+          <t>-16,54; 8,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 20,69</t>
+          <t>-0,42; 22,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 16,07</t>
+          <t>-3,49; 16,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 9,09</t>
+          <t>-11,57; 8,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 17,26</t>
+          <t>-1,47; 17,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 99,61</t>
+          <t>-28,74; 92,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 86,61</t>
+          <t>-26,88; 79,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 88,44</t>
+          <t>-23,05; 90,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 70,67</t>
+          <t>-13,78; 61,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 33,47</t>
+          <t>-37,16; 29,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 69,7</t>
+          <t>-1,16; 81,33</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 56,54</t>
+          <t>-8,07; 59,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 33,45</t>
+          <t>-28,22; 28,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,98; 62,72</t>
+          <t>-3,36; 60,54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41,86</t>
+          <t>42,19</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,82</t>
+          <t>11,96</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,1</t>
+          <t>12,24</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 0,0</t>
+          <t>-96,53; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 84,85</t>
+          <t>-29,46; 84,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 10,35</t>
+          <t>-3,36; 9,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 9,91</t>
+          <t>-5,73; 9,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,29; 18,24</t>
+          <t>5,8; 18,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 9,79</t>
+          <t>-3,64; 9,54</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 9,93</t>
+          <t>-4,29; 9,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,38; 17,95</t>
+          <t>6,07; 18,71</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166,86%</t>
+          <t>168,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 34,39</t>
+          <t>-9,44; 30,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 32,04</t>
+          <t>-14,57; 31,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,01; 58,89</t>
+          <t>15,22; 60,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 31,99</t>
+          <t>-9,75; 30,57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 32,67</t>
+          <t>-11,94; 30,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16,83; 58,27</t>
+          <t>16,38; 61,63</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>3,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 5,61</t>
+          <t>-4,99; 5,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,52; -0,44</t>
+          <t>-9,88; -0,66</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,72</t>
+          <t>-6,19; 2,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 9,2</t>
+          <t>-1,37; 9,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 6,19</t>
+          <t>-4,47; 6,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 8,4</t>
+          <t>2,41; 11,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,55</t>
+          <t>-1,27; 6,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,52</t>
+          <t>-4,96; 2,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 4,62</t>
+          <t>-0,31; 6,21</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-3,51%</t>
+          <t>-5,85%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-3,98%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 24,43</t>
+          <t>-17,2; 24,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,68; -1,24</t>
+          <t>-34,58; -1,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 16,44</t>
+          <t>-21,0; 12,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 29,28</t>
+          <t>-3,79; 28,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 19,09</t>
+          <t>-11,49; 20,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 25,05</t>
+          <t>6,3; 36,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 22,37</t>
+          <t>-3,75; 23,08</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 9,23</t>
+          <t>-15,46; 7,77</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 15,36</t>
+          <t>-0,9; 21,27</t>
         </is>
       </c>
     </row>
